--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4245,7 +4245,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -4794,6 +4794,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4803,7 +4806,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5352,6 +5355,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>366000</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>368000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5394,7 +5400,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -5943,6 +5949,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5952,7 +5961,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6501,6 +6510,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>578877.12606147851</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>597236.24273614574</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6543,7 +6555,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7092,6 +7104,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>45989</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>46022</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7101,7 +7116,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="183"/>
+                <c:ptCount val="184"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7650,6 +7665,9 @@
                 </c:pt>
                 <c:pt idx="182">
                   <c:v>212877.12606147851</c:v>
+                </c:pt>
+                <c:pt idx="183">
+                  <c:v>229236.24273614574</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7671,11 +7689,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="532129664"/>
-        <c:axId val="539234688"/>
+        <c:axId val="154698496"/>
+        <c:axId val="154700416"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="532129664"/>
+        <c:axId val="154698496"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7718,14 +7736,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="539234688"/>
+        <c:crossAx val="154700416"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="539234688"/>
+        <c:axId val="154700416"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7776,7 +7794,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="532129664"/>
+        <c:crossAx val="154698496"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8182,7 +8200,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB185"/>
+  <dimension ref="A1:AB186"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16040,6 +16058,39 @@
       <c r="J185" s="31">
         <f>VLOOKUP(A185,myPEPB!B:C,2)</f>
         <v>14.670000079999999</v>
+      </c>
+    </row>
+    <row r="186" spans="1:10" ht="12.75">
+      <c r="A186" s="13">
+        <v>46022</v>
+      </c>
+      <c r="B186" s="14">
+        <v>2.9221650390625</v>
+      </c>
+      <c r="C186" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D186" s="16">
+        <v>684.42403945864999</v>
+      </c>
+      <c r="E186" s="16">
+        <v>204381.42088228982</v>
+      </c>
+      <c r="F186" s="16">
+        <v>597236.24273614574</v>
+      </c>
+      <c r="G186" s="16">
+        <v>368000</v>
+      </c>
+      <c r="H186" s="16">
+        <v>597236.24273614574</v>
+      </c>
+      <c r="I186" s="16">
+        <v>229236.24273614574</v>
+      </c>
+      <c r="J186" s="31">
+        <f>VLOOKUP(A186,myPEPB!B:C,2)</f>
+        <v>15.5</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="911" uniqueCount="906">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="924">
   <si>
     <t>PE</t>
   </si>
@@ -3631,6 +3631,78 @@
   </si>
   <si>
     <t xml:space="preserve">2025/11/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/1/28
 </t>
   </si>
 </sst>
@@ -7689,11 +7761,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="154698496"/>
-        <c:axId val="154700416"/>
+        <c:axId val="527741696"/>
+        <c:axId val="546274304"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="154698496"/>
+        <c:axId val="527741696"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7736,14 +7808,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154700416"/>
+        <c:crossAx val="546274304"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="154700416"/>
+        <c:axId val="546274304"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7794,7 +7866,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="154698496"/>
+        <c:crossAx val="527741696"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16106,7 +16178,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1151"/>
+  <dimension ref="A1:D1171"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -34149,7 +34221,7 @@
     </row>
     <row r="1129" spans="1:4">
       <c r="A1129" s="17">
-        <f t="shared" ref="A1129:A1151" si="8">A1128+1</f>
+        <f t="shared" ref="A1129:A1171" si="8">A1128+1</f>
         <v>1127</v>
       </c>
       <c r="B1129" s="37">
@@ -34513,6 +34585,326 @@
       <c r="D1151" s="17">
         <f>SUM(C$3:C1151)/A1151</f>
         <v>12.350804010109771</v>
+      </c>
+    </row>
+    <row r="1152" spans="1:4">
+      <c r="A1152" s="17">
+        <f t="shared" si="8"/>
+        <v>1150</v>
+      </c>
+      <c r="B1152" s="37" t="s">
+        <v>906</v>
+      </c>
+      <c r="C1152" s="38">
+        <v>15.729999542236328</v>
+      </c>
+      <c r="D1152" s="17">
+        <f>SUM(C$3:C1152)/A1152</f>
+        <v>12.353742441007272</v>
+      </c>
+    </row>
+    <row r="1153" spans="1:4">
+      <c r="A1153" s="17">
+        <f t="shared" si="8"/>
+        <v>1151</v>
+      </c>
+      <c r="B1153" s="37" t="s">
+        <v>907</v>
+      </c>
+      <c r="C1153" s="38">
+        <v>15.949999809265137</v>
+      </c>
+      <c r="D1153" s="17">
+        <f>SUM(C$3:C1153)/A1153</f>
+        <v>12.356866904402805</v>
+      </c>
+    </row>
+    <row r="1154" spans="1:4">
+      <c r="A1154" s="17">
+        <f t="shared" si="8"/>
+        <v>1152</v>
+      </c>
+      <c r="B1154" s="37" t="s">
+        <v>908</v>
+      </c>
+      <c r="C1154" s="38">
+        <v>15.880000114440918</v>
+      </c>
+      <c r="D1154" s="17">
+        <f>SUM(C$3:C1154)/A1154</f>
+        <v>12.35992517975874</v>
+      </c>
+    </row>
+    <row r="1155" spans="1:4">
+      <c r="A1155" s="17">
+        <f t="shared" si="8"/>
+        <v>1153</v>
+      </c>
+      <c r="B1155" s="37" t="s">
+        <v>909</v>
+      </c>
+      <c r="C1155" s="38">
+        <v>15.760000228881836</v>
+      </c>
+      <c r="D1155" s="17">
+        <f>SUM(C$3:C1155)/A1155</f>
+        <v>12.362874073990417</v>
+      </c>
+    </row>
+    <row r="1156" spans="1:4">
+      <c r="A1156" s="17">
+        <f t="shared" si="8"/>
+        <v>1154</v>
+      </c>
+      <c r="B1156" s="37" t="s">
+        <v>910</v>
+      </c>
+      <c r="C1156" s="38">
+        <v>15.850000381469727</v>
+      </c>
+      <c r="D1156" s="17">
+        <f>SUM(C$3:C1156)/A1156</f>
+        <v>12.365895847220468</v>
+      </c>
+    </row>
+    <row r="1157" spans="1:4">
+      <c r="A1157" s="17">
+        <f t="shared" si="8"/>
+        <v>1155</v>
+      </c>
+      <c r="B1157" s="37" t="s">
+        <v>911</v>
+      </c>
+      <c r="C1157" s="38">
+        <v>15.920000076293945</v>
+      </c>
+      <c r="D1157" s="17">
+        <f>SUM(C$3:C1157)/A1157</f>
+        <v>12.368972993739147</v>
+      </c>
+    </row>
+    <row r="1158" spans="1:4">
+      <c r="A1158" s="17">
+        <f t="shared" si="8"/>
+        <v>1156</v>
+      </c>
+      <c r="B1158" s="37" t="s">
+        <v>912</v>
+      </c>
+      <c r="C1158" s="38">
+        <v>15.869999885559082</v>
+      </c>
+      <c r="D1158" s="17">
+        <f>SUM(C$3:C1158)/A1158</f>
+        <v>12.37200156371477</v>
+      </c>
+    </row>
+    <row r="1159" spans="1:4">
+      <c r="A1159" s="17">
+        <f t="shared" si="8"/>
+        <v>1157</v>
+      </c>
+      <c r="B1159" s="37" t="s">
+        <v>913</v>
+      </c>
+      <c r="C1159" s="38">
+        <v>15.770000457763672</v>
+      </c>
+      <c r="D1159" s="17">
+        <f>SUM(C$3:C1159)/A1159</f>
+        <v>12.374938468549731</v>
+      </c>
+    </row>
+    <row r="1160" spans="1:4">
+      <c r="A1160" s="17">
+        <f t="shared" si="8"/>
+        <v>1158</v>
+      </c>
+      <c r="B1160" s="37" t="s">
+        <v>914</v>
+      </c>
+      <c r="C1160" s="38">
+        <v>15.779999732971191</v>
+      </c>
+      <c r="D1160" s="17">
+        <f>SUM(C$3:C1160)/A1160</f>
+        <v>12.377878935962874</v>
+      </c>
+    </row>
+    <row r="1161" spans="1:4">
+      <c r="A1161" s="17">
+        <f t="shared" si="8"/>
+        <v>1159</v>
+      </c>
+      <c r="B1161" s="37" t="s">
+        <v>915</v>
+      </c>
+      <c r="C1161" s="38">
+        <v>15.699999809265137</v>
+      </c>
+      <c r="D1161" s="17">
+        <f>SUM(C$3:C1161)/A1161</f>
+        <v>12.38074530427461</v>
+      </c>
+    </row>
+    <row r="1162" spans="1:4">
+      <c r="A1162" s="17">
+        <f t="shared" si="8"/>
+        <v>1160</v>
+      </c>
+      <c r="B1162" s="37" t="s">
+        <v>916</v>
+      </c>
+      <c r="C1162" s="38">
+        <v>15.710000038146973</v>
+      </c>
+      <c r="D1162" s="17">
+        <f>SUM(C$3:C1162)/A1162</f>
+        <v>12.383615351458984</v>
+      </c>
+    </row>
+    <row r="1163" spans="1:4">
+      <c r="A1163" s="17">
+        <f t="shared" si="8"/>
+        <v>1161</v>
+      </c>
+      <c r="B1163" s="37" t="s">
+        <v>917</v>
+      </c>
+      <c r="C1163" s="38">
+        <v>15.710000038146973</v>
+      </c>
+      <c r="D1163" s="17">
+        <f>SUM(C$3:C1163)/A1163</f>
+        <v>12.386480454548293</v>
+      </c>
+    </row>
+    <row r="1164" spans="1:4">
+      <c r="A1164" s="17">
+        <f t="shared" si="8"/>
+        <v>1162</v>
+      </c>
+      <c r="B1164" s="37" t="s">
+        <v>918</v>
+      </c>
+      <c r="C1164" s="38">
+        <v>15.659999847412109</v>
+      </c>
+      <c r="D1164" s="17">
+        <f>SUM(C$3:C1164)/A1164</f>
+        <v>12.389297596882944</v>
+      </c>
+    </row>
+    <row r="1165" spans="1:4">
+      <c r="A1165" s="17">
+        <f t="shared" si="8"/>
+        <v>1163</v>
+      </c>
+      <c r="B1165" s="37" t="s">
+        <v>919</v>
+      </c>
+      <c r="C1165" s="38">
+        <v>15.659999847412109</v>
+      </c>
+      <c r="D1165" s="17">
+        <f>SUM(C$3:C1165)/A1165</f>
+        <v>12.392109894604808</v>
+      </c>
+    </row>
+    <row r="1166" spans="1:4">
+      <c r="A1166" s="17">
+        <f t="shared" si="8"/>
+        <v>1164</v>
+      </c>
+      <c r="B1166" s="37" t="s">
+        <v>920</v>
+      </c>
+      <c r="C1166" s="38">
+        <v>15.600000381469727</v>
+      </c>
+      <c r="D1166" s="17">
+        <f>SUM(C$3:C1166)/A1166</f>
+        <v>12.394865814267064</v>
+      </c>
+    </row>
+    <row r="1167" spans="1:4">
+      <c r="A1167" s="17">
+        <f t="shared" si="8"/>
+        <v>1165</v>
+      </c>
+      <c r="B1167" s="37" t="s">
+        <v>921</v>
+      </c>
+      <c r="C1167" s="38">
+        <v>15.670000076293945</v>
+      </c>
+      <c r="D1167" s="17">
+        <f>SUM(C$3:C1167)/A1167</f>
+        <v>12.397677088311722</v>
+      </c>
+    </row>
+    <row r="1168" spans="1:4">
+      <c r="A1168" s="17">
+        <f t="shared" si="8"/>
+        <v>1166</v>
+      </c>
+      <c r="B1168" s="37" t="s">
+        <v>922</v>
+      </c>
+      <c r="C1168" s="38">
+        <v>15.680000305175781</v>
+      </c>
+      <c r="D1168" s="17">
+        <f>SUM(C$3:C1168)/A1168</f>
+        <v>12.400492116799597</v>
+      </c>
+    </row>
+    <row r="1169" spans="1:4">
+      <c r="A1169" s="17">
+        <f t="shared" si="8"/>
+        <v>1167</v>
+      </c>
+      <c r="B1169" s="37" t="s">
+        <v>923</v>
+      </c>
+      <c r="C1169" s="38">
+        <v>15.720000267028809</v>
+      </c>
+      <c r="D1169" s="17">
+        <f>SUM(C$3:C1169)/A1169</f>
+        <v>12.403336596791226</v>
+      </c>
+    </row>
+    <row r="1170" spans="1:4">
+      <c r="A1170" s="17">
+        <f t="shared" si="8"/>
+        <v>1168</v>
+      </c>
+      <c r="B1170" s="37">
+        <v>46051</v>
+      </c>
+      <c r="C1170" s="38">
+        <v>15.829999923706055</v>
+      </c>
+      <c r="D1170" s="17">
+        <f>SUM(C$3:C1170)/A1170</f>
+        <v>12.406270383886188</v>
+      </c>
+    </row>
+    <row r="1171" spans="1:4">
+      <c r="A1171" s="17">
+        <f t="shared" si="8"/>
+        <v>1169</v>
+      </c>
+      <c r="B1171" s="37">
+        <v>46052</v>
+      </c>
+      <c r="C1171" s="38">
+        <v>15.68999958</v>
+      </c>
+      <c r="D1171" s="17">
+        <f>SUM(C$3:C1171)/A1171</f>
+        <v>12.409079390897405</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4317,7 +4317,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -4869,6 +4869,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4878,7 +4881,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5430,6 +5433,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>368000</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>370000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5472,7 +5478,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -6024,6 +6030,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6033,7 +6042,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6585,6 +6594,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>597236.24273614574</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>612657.55549572455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6627,7 +6639,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7179,6 +7191,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>46022</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>46052</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7188,7 +7203,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="184"/>
+                <c:ptCount val="185"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7740,6 +7755,9 @@
                 </c:pt>
                 <c:pt idx="183">
                   <c:v>229236.24273614574</c:v>
+                </c:pt>
+                <c:pt idx="184">
+                  <c:v>242657.55549572455</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7761,11 +7779,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="527741696"/>
-        <c:axId val="546274304"/>
+        <c:axId val="90701184"/>
+        <c:axId val="397238272"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="527741696"/>
+        <c:axId val="90701184"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7808,14 +7826,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="546274304"/>
+        <c:crossAx val="397238272"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="546274304"/>
+        <c:axId val="397238272"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7866,7 +7884,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="527741696"/>
+        <c:crossAx val="90701184"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8272,7 +8290,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB186"/>
+  <dimension ref="A1:AB187"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16163,6 +16181,39 @@
       <c r="J186" s="31">
         <f>VLOOKUP(A186,myPEPB!B:C,2)</f>
         <v>15.5</v>
+      </c>
+    </row>
+    <row r="187" spans="1:10" ht="12.75">
+      <c r="A187" s="13">
+        <v>46052</v>
+      </c>
+      <c r="B187" s="14">
+        <v>2.9878330078125002</v>
+      </c>
+      <c r="C187" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D187" s="16">
+        <v>669.38145296957941</v>
+      </c>
+      <c r="E187" s="16">
+        <v>205050.80233525939</v>
+      </c>
+      <c r="F187" s="16">
+        <v>612657.55549572455</v>
+      </c>
+      <c r="G187" s="16">
+        <v>370000</v>
+      </c>
+      <c r="H187" s="16">
+        <v>612657.55549572455</v>
+      </c>
+      <c r="I187" s="16">
+        <v>242657.55549572455</v>
+      </c>
+      <c r="J187" s="31">
+        <f>VLOOKUP(A187,myPEPB!B:C,2)</f>
+        <v>15.68999958</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="929" uniqueCount="924">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="936">
   <si>
     <t>PE</t>
   </si>
@@ -3703,6 +3703,54 @@
   </si>
   <si>
     <t xml:space="preserve">2026/1/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/2/25
 </t>
   </si>
 </sst>
@@ -7779,11 +7827,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="90701184"/>
-        <c:axId val="397238272"/>
+        <c:axId val="443524608"/>
+        <c:axId val="443526528"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="90701184"/>
+        <c:axId val="443524608"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7826,14 +7874,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="397238272"/>
+        <c:crossAx val="443526528"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="397238272"/>
+        <c:axId val="443526528"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7884,7 +7932,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="90701184"/>
+        <c:crossAx val="443524608"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16229,7 +16277,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1171"/>
+  <dimension ref="A1:D1185"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -34272,7 +34320,7 @@
     </row>
     <row r="1129" spans="1:4">
       <c r="A1129" s="17">
-        <f t="shared" ref="A1129:A1171" si="8">A1128+1</f>
+        <f t="shared" ref="A1129:A1185" si="8">A1128+1</f>
         <v>1127</v>
       </c>
       <c r="B1129" s="37">
@@ -34956,6 +35004,230 @@
       <c r="D1171" s="17">
         <f>SUM(C$3:C1171)/A1171</f>
         <v>12.409079390897405</v>
+      </c>
+    </row>
+    <row r="1172" spans="1:4">
+      <c r="A1172" s="17">
+        <f t="shared" si="8"/>
+        <v>1170</v>
+      </c>
+      <c r="B1172" s="37" t="s">
+        <v>924</v>
+      </c>
+      <c r="C1172" s="38">
+        <v>15.35999966</v>
+      </c>
+      <c r="D1172" s="17">
+        <f>SUM(C$3:C1172)/A1172</f>
+        <v>12.411601544973561</v>
+      </c>
+    </row>
+    <row r="1173" spans="1:4">
+      <c r="A1173" s="17">
+        <f t="shared" si="8"/>
+        <v>1171</v>
+      </c>
+      <c r="B1173" s="37" t="s">
+        <v>925</v>
+      </c>
+      <c r="C1173" s="38">
+        <v>15.52000046</v>
+      </c>
+      <c r="D1173" s="17">
+        <f>SUM(C$3:C1173)/A1173</f>
+        <v>12.414256027394591</v>
+      </c>
+    </row>
+    <row r="1174" spans="1:4">
+      <c r="A1174" s="17">
+        <f t="shared" si="8"/>
+        <v>1172</v>
+      </c>
+      <c r="B1174" s="37" t="s">
+        <v>926</v>
+      </c>
+      <c r="C1174" s="38">
+        <v>15.68999958</v>
+      </c>
+      <c r="D1174" s="17">
+        <f>SUM(C$3:C1174)/A1174</f>
+        <v>12.417051030425824</v>
+      </c>
+    </row>
+    <row r="1175" spans="1:4">
+      <c r="A1175" s="17">
+        <f t="shared" si="8"/>
+        <v>1173</v>
+      </c>
+      <c r="B1175" s="37" t="s">
+        <v>927</v>
+      </c>
+      <c r="C1175" s="38">
+        <v>15.600000380000001</v>
+      </c>
+      <c r="D1175" s="17">
+        <f>SUM(C$3:C1175)/A1175</f>
+        <v>12.419764542232793</v>
+      </c>
+    </row>
+    <row r="1176" spans="1:4">
+      <c r="A1176" s="17">
+        <f t="shared" si="8"/>
+        <v>1174</v>
+      </c>
+      <c r="B1176" s="37" t="s">
+        <v>928</v>
+      </c>
+      <c r="C1176" s="38">
+        <v>15.56999969</v>
+      </c>
+      <c r="D1176" s="17">
+        <f>SUM(C$3:C1176)/A1176</f>
+        <v>12.42244787711164</v>
+      </c>
+    </row>
+    <row r="1177" spans="1:4">
+      <c r="A1177" s="17">
+        <f t="shared" si="8"/>
+        <v>1175</v>
+      </c>
+      <c r="B1177" s="37" t="s">
+        <v>929</v>
+      </c>
+      <c r="C1177" s="38">
+        <v>15.760000229999999</v>
+      </c>
+      <c r="D1177" s="17">
+        <f>SUM(C$3:C1177)/A1177</f>
+        <v>12.425288347199205</v>
+      </c>
+    </row>
+    <row r="1178" spans="1:4">
+      <c r="A1178" s="17">
+        <f t="shared" si="8"/>
+        <v>1176</v>
+      </c>
+      <c r="B1178" s="37" t="s">
+        <v>930</v>
+      </c>
+      <c r="C1178" s="38">
+        <v>15.760000229999999</v>
+      </c>
+      <c r="D1178" s="17">
+        <f>SUM(C$3:C1178)/A1178</f>
+        <v>12.428123986555329</v>
+      </c>
+    </row>
+    <row r="1179" spans="1:4">
+      <c r="A1179" s="17">
+        <f t="shared" si="8"/>
+        <v>1177</v>
+      </c>
+      <c r="B1179" s="37" t="s">
+        <v>931</v>
+      </c>
+      <c r="C1179" s="38">
+        <v>15.77000046</v>
+      </c>
+      <c r="D1179" s="17">
+        <f>SUM(C$3:C1179)/A1179</f>
+        <v>12.430963303864967</v>
+      </c>
+    </row>
+    <row r="1180" spans="1:4">
+      <c r="A1180" s="17">
+        <f t="shared" si="8"/>
+        <v>1178</v>
+      </c>
+      <c r="B1180" s="37" t="s">
+        <v>932</v>
+      </c>
+      <c r="C1180" s="38">
+        <v>15.77000046</v>
+      </c>
+      <c r="D1180" s="17">
+        <f>SUM(C$3:C1180)/A1180</f>
+        <v>12.433797800601923</v>
+      </c>
+    </row>
+    <row r="1181" spans="1:4">
+      <c r="A1181" s="17">
+        <f t="shared" si="8"/>
+        <v>1179</v>
+      </c>
+      <c r="B1181" s="37" t="s">
+        <v>933</v>
+      </c>
+      <c r="C1181" s="38">
+        <v>15.510000229999999</v>
+      </c>
+      <c r="D1181" s="17">
+        <f>SUM(C$3:C1181)/A1181</f>
+        <v>12.436406962967824</v>
+      </c>
+    </row>
+    <row r="1182" spans="1:4">
+      <c r="A1182" s="17">
+        <f t="shared" si="8"/>
+        <v>1180</v>
+      </c>
+      <c r="B1182" s="37" t="s">
+        <v>934</v>
+      </c>
+      <c r="C1182" s="38">
+        <v>15.670000079999999</v>
+      </c>
+      <c r="D1182" s="17">
+        <f>SUM(C$3:C1182)/A1182</f>
+        <v>12.439147296117852</v>
+      </c>
+    </row>
+    <row r="1183" spans="1:4">
+      <c r="A1183" s="17">
+        <f t="shared" si="8"/>
+        <v>1181</v>
+      </c>
+      <c r="B1183" s="37" t="s">
+        <v>935</v>
+      </c>
+      <c r="C1183" s="38">
+        <v>15.739999770000001</v>
+      </c>
+      <c r="D1183" s="17">
+        <f>SUM(C$3:C1183)/A1183</f>
+        <v>12.441942260109284</v>
+      </c>
+    </row>
+    <row r="1184" spans="1:4">
+      <c r="A1184" s="17">
+        <f t="shared" si="8"/>
+        <v>1182</v>
+      </c>
+      <c r="B1184" s="37">
+        <v>46079</v>
+      </c>
+      <c r="C1184" s="38">
+        <v>15.670000079999999</v>
+      </c>
+      <c r="D1184" s="17">
+        <f>SUM(C$3:C1184)/A1184</f>
+        <v>12.444673273493285</v>
+      </c>
+    </row>
+    <row r="1185" spans="1:4">
+      <c r="A1185" s="17">
+        <f t="shared" si="8"/>
+        <v>1183</v>
+      </c>
+      <c r="B1185" s="37">
+        <v>46080</v>
+      </c>
+      <c r="C1185" s="38">
+        <v>15.64000034</v>
+      </c>
+      <c r="D1185" s="17">
+        <f>SUM(C$3:C1185)/A1185</f>
+        <v>12.447374310743079</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4365,7 +4365,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -4920,6 +4920,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -4929,7 +4932,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5484,6 +5487,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>370000</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>372000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5526,7 +5532,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -6081,6 +6087,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6090,7 +6099,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6645,6 +6654,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>612657.55549572455</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>615439.812291938</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6687,7 +6699,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7242,6 +7254,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>46052</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>46080</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7251,7 +7266,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="185"/>
+                <c:ptCount val="186"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7806,6 +7821,9 @@
                 </c:pt>
                 <c:pt idx="184">
                   <c:v>242657.55549572455</c:v>
+                </c:pt>
+                <c:pt idx="185">
+                  <c:v>243439.812291938</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7827,11 +7845,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="443524608"/>
-        <c:axId val="443526528"/>
+        <c:axId val="77542144"/>
+        <c:axId val="77543680"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="443524608"/>
+        <c:axId val="77542144"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7874,14 +7892,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443526528"/>
+        <c:crossAx val="77543680"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="443526528"/>
+        <c:axId val="77543680"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7932,7 +7950,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="443524608"/>
+        <c:crossAx val="77542144"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8338,7 +8356,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB187"/>
+  <dimension ref="A1:AB188"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16262,6 +16280,39 @@
       <c r="J187" s="31">
         <f>VLOOKUP(A187,myPEPB!B:C,2)</f>
         <v>15.68999958</v>
+      </c>
+    </row>
+    <row r="188" spans="1:10" ht="12.75">
+      <c r="A188" s="13">
+        <v>46080</v>
+      </c>
+      <c r="B188" s="14">
+        <v>2.9916479492187502</v>
+      </c>
+      <c r="C188" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D188" s="16">
+        <v>668.52785954386354</v>
+      </c>
+      <c r="E188" s="16">
+        <v>205719.33019480325</v>
+      </c>
+      <c r="F188" s="16">
+        <v>615439.812291938</v>
+      </c>
+      <c r="G188" s="16">
+        <v>372000</v>
+      </c>
+      <c r="H188" s="16">
+        <v>615439.812291938</v>
+      </c>
+      <c r="I188" s="16">
+        <v>243439.812291938</v>
+      </c>
+      <c r="J188" s="31">
+        <f>VLOOKUP(A188,myPEPB!B:C,2)</f>
+        <v>15.64000034</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="941" uniqueCount="936">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
   <si>
     <t>PE</t>
   </si>
@@ -3751,6 +3751,86 @@
   </si>
   <si>
     <t xml:space="preserve">2026/2/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/3/27
 </t>
   </si>
 </sst>
@@ -7845,11 +7925,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="77542144"/>
-        <c:axId val="77543680"/>
+        <c:axId val="480350208"/>
+        <c:axId val="480351744"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="77542144"/>
+        <c:axId val="480350208"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7892,14 +7972,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77543680"/>
+        <c:crossAx val="480351744"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="77543680"/>
+        <c:axId val="480351744"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7950,7 +8030,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="77542144"/>
+        <c:crossAx val="480350208"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16328,7 +16408,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1185"/>
+  <dimension ref="A1:D1207"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -34371,7 +34451,7 @@
     </row>
     <row r="1129" spans="1:4">
       <c r="A1129" s="17">
-        <f t="shared" ref="A1129:A1185" si="8">A1128+1</f>
+        <f t="shared" ref="A1129:A1207" si="8">A1128+1</f>
         <v>1127</v>
       </c>
       <c r="B1129" s="37">
@@ -35279,6 +35359,358 @@
       <c r="D1185" s="17">
         <f>SUM(C$3:C1185)/A1185</f>
         <v>12.447374310743079</v>
+      </c>
+    </row>
+    <row r="1186" spans="1:4">
+      <c r="A1186" s="17">
+        <f t="shared" si="8"/>
+        <v>1184</v>
+      </c>
+      <c r="B1186" s="37" t="s">
+        <v>936</v>
+      </c>
+      <c r="C1186" s="38">
+        <v>15.80000019</v>
+      </c>
+      <c r="D1186" s="17">
+        <f>SUM(C$3:C1186)/A1186</f>
+        <v>12.450205920438398</v>
+      </c>
+    </row>
+    <row r="1187" spans="1:4">
+      <c r="A1187" s="17">
+        <f t="shared" si="8"/>
+        <v>1185</v>
+      </c>
+      <c r="B1187" s="37" t="s">
+        <v>937</v>
+      </c>
+      <c r="C1187" s="38">
+        <v>15.760000229999999</v>
+      </c>
+      <c r="D1187" s="17">
+        <f>SUM(C$3:C1187)/A1187</f>
+        <v>12.452998995805117</v>
+      </c>
+    </row>
+    <row r="1188" spans="1:4">
+      <c r="A1188" s="17">
+        <f t="shared" si="8"/>
+        <v>1186</v>
+      </c>
+      <c r="B1188" s="37" t="s">
+        <v>938</v>
+      </c>
+      <c r="C1188" s="38">
+        <v>15.579999920000001</v>
+      </c>
+      <c r="D1188" s="17">
+        <f>SUM(C$3:C1188)/A1188</f>
+        <v>12.455635590176277</v>
+      </c>
+    </row>
+    <row r="1189" spans="1:4">
+      <c r="A1189" s="17">
+        <f t="shared" si="8"/>
+        <v>1187</v>
+      </c>
+      <c r="B1189" s="37" t="s">
+        <v>939</v>
+      </c>
+      <c r="C1189" s="38">
+        <v>15.649999619999999</v>
+      </c>
+      <c r="D1189" s="17">
+        <f>SUM(C$3:C1189)/A1189</f>
+        <v>12.45832671404302</v>
+      </c>
+    </row>
+    <row r="1190" spans="1:4">
+      <c r="A1190" s="17">
+        <f t="shared" si="8"/>
+        <v>1188</v>
+      </c>
+      <c r="B1190" s="37" t="s">
+        <v>940</v>
+      </c>
+      <c r="C1190" s="38">
+        <v>15.65999985</v>
+      </c>
+      <c r="D1190" s="17">
+        <f>SUM(C$3:C1190)/A1190</f>
+        <v>12.461021725100222</v>
+      </c>
+    </row>
+    <row r="1191" spans="1:4">
+      <c r="A1191" s="17">
+        <f t="shared" si="8"/>
+        <v>1189</v>
+      </c>
+      <c r="B1191" s="37" t="s">
+        <v>941</v>
+      </c>
+      <c r="C1191" s="38">
+        <v>15.579999920000001</v>
+      </c>
+      <c r="D1191" s="17">
+        <f>SUM(C$3:C1191)/A1191</f>
+        <v>12.46364491954505</v>
+      </c>
+    </row>
+    <row r="1192" spans="1:4">
+      <c r="A1192" s="17">
+        <f t="shared" si="8"/>
+        <v>1190</v>
+      </c>
+      <c r="B1192" s="37" t="s">
+        <v>942</v>
+      </c>
+      <c r="C1192" s="38">
+        <v>15.579999920000001</v>
+      </c>
+      <c r="D1192" s="17">
+        <f>SUM(C$3:C1192)/A1192</f>
+        <v>12.466263705259719</v>
+      </c>
+    </row>
+    <row r="1193" spans="1:4">
+      <c r="A1193" s="17">
+        <f t="shared" si="8"/>
+        <v>1191</v>
+      </c>
+      <c r="B1193" s="37" t="s">
+        <v>943</v>
+      </c>
+      <c r="C1193" s="38">
+        <v>15.81999969</v>
+      </c>
+      <c r="D1193" s="17">
+        <f>SUM(C$3:C1193)/A1193</f>
+        <v>12.46907960449124</v>
+      </c>
+    </row>
+    <row r="1194" spans="1:4">
+      <c r="A1194" s="17">
+        <f t="shared" si="8"/>
+        <v>1192</v>
+      </c>
+      <c r="B1194" s="37" t="s">
+        <v>944</v>
+      </c>
+      <c r="C1194" s="38">
+        <v>15.80000019</v>
+      </c>
+      <c r="D1194" s="17">
+        <f>SUM(C$3:C1194)/A1194</f>
+        <v>12.471874000955593</v>
+      </c>
+    </row>
+    <row r="1195" spans="1:4">
+      <c r="A1195" s="17">
+        <f t="shared" si="8"/>
+        <v>1193</v>
+      </c>
+      <c r="B1195" s="37" t="s">
+        <v>945</v>
+      </c>
+      <c r="C1195" s="38">
+        <v>15.72000027</v>
+      </c>
+      <c r="D1195" s="17">
+        <f>SUM(C$3:C1195)/A1195</f>
+        <v>12.474596654995025</v>
+      </c>
+    </row>
+    <row r="1196" spans="1:4">
+      <c r="A1196" s="17">
+        <f t="shared" si="8"/>
+        <v>1194</v>
+      </c>
+      <c r="B1196" s="37" t="s">
+        <v>946</v>
+      </c>
+      <c r="C1196" s="38">
+        <v>15.72999954</v>
+      </c>
+      <c r="D1196" s="17">
+        <f>SUM(C$3:C1196)/A1196</f>
+        <v>12.477323123072919</v>
+      </c>
+    </row>
+    <row r="1197" spans="1:4">
+      <c r="A1197" s="17">
+        <f t="shared" si="8"/>
+        <v>1195</v>
+      </c>
+      <c r="B1197" s="37" t="s">
+        <v>947</v>
+      </c>
+      <c r="C1197" s="38">
+        <v>15.64000034</v>
+      </c>
+      <c r="D1197" s="17">
+        <f>SUM(C$3:C1197)/A1197</f>
+        <v>12.479969714886247</v>
+      </c>
+    </row>
+    <row r="1198" spans="1:4">
+      <c r="A1198" s="17">
+        <f t="shared" si="8"/>
+        <v>1196</v>
+      </c>
+      <c r="B1198" s="37" t="s">
+        <v>948</v>
+      </c>
+      <c r="C1198" s="38">
+        <v>15.68000031</v>
+      </c>
+      <c r="D1198" s="17">
+        <f>SUM(C$3:C1198)/A1198</f>
+        <v>12.482645325751728</v>
+      </c>
+    </row>
+    <row r="1199" spans="1:4">
+      <c r="A1199" s="17">
+        <f t="shared" si="8"/>
+        <v>1197</v>
+      </c>
+      <c r="B1199" s="37" t="s">
+        <v>949</v>
+      </c>
+      <c r="C1199" s="38">
+        <v>15.5</v>
+      </c>
+      <c r="D1199" s="17">
+        <f>SUM(C$3:C1199)/A1199</f>
+        <v>12.485166089890615</v>
+      </c>
+    </row>
+    <row r="1200" spans="1:4">
+      <c r="A1200" s="17">
+        <f t="shared" si="8"/>
+        <v>1198</v>
+      </c>
+      <c r="B1200" s="37" t="s">
+        <v>950</v>
+      </c>
+      <c r="C1200" s="38">
+        <v>15.5</v>
+      </c>
+      <c r="D1200" s="17">
+        <f>SUM(C$3:C1200)/A1200</f>
+        <v>12.487682645742124</v>
+      </c>
+    </row>
+    <row r="1201" spans="1:4">
+      <c r="A1201" s="17">
+        <f t="shared" si="8"/>
+        <v>1199</v>
+      </c>
+      <c r="B1201" s="37" t="s">
+        <v>951</v>
+      </c>
+      <c r="C1201" s="38">
+        <v>14.94999981</v>
+      </c>
+      <c r="D1201" s="17">
+        <f>SUM(C$3:C1201)/A1201</f>
+        <v>12.489736288080955</v>
+      </c>
+    </row>
+    <row r="1202" spans="1:4">
+      <c r="A1202" s="17">
+        <f t="shared" si="8"/>
+        <v>1200</v>
+      </c>
+      <c r="B1202" s="37" t="s">
+        <v>952</v>
+      </c>
+      <c r="C1202" s="38">
+        <v>15.09000015</v>
+      </c>
+      <c r="D1202" s="17">
+        <f>SUM(C$3:C1202)/A1202</f>
+        <v>12.491903174632554</v>
+      </c>
+    </row>
+    <row r="1203" spans="1:4">
+      <c r="A1203" s="17">
+        <f t="shared" si="8"/>
+        <v>1201</v>
+      </c>
+      <c r="B1203" s="37" t="s">
+        <v>953</v>
+      </c>
+      <c r="C1203" s="38">
+        <v>15.260000229999999</v>
+      </c>
+      <c r="D1203" s="17">
+        <f>SUM(C$3:C1203)/A1203</f>
+        <v>12.494208001489646</v>
+      </c>
+    </row>
+    <row r="1204" spans="1:4">
+      <c r="A1204" s="17">
+        <f t="shared" si="8"/>
+        <v>1202</v>
+      </c>
+      <c r="B1204" s="37" t="s">
+        <v>954</v>
+      </c>
+      <c r="C1204" s="38">
+        <v>15.100000380000001</v>
+      </c>
+      <c r="D1204" s="17">
+        <f>SUM(C$3:C1204)/A1204</f>
+        <v>12.496375882004214</v>
+      </c>
+    </row>
+    <row r="1205" spans="1:4">
+      <c r="A1205" s="17">
+        <f t="shared" si="8"/>
+        <v>1203</v>
+      </c>
+      <c r="B1205" s="37" t="s">
+        <v>955</v>
+      </c>
+      <c r="C1205" s="38">
+        <v>15.18000031</v>
+      </c>
+      <c r="D1205" s="17">
+        <f>SUM(C$3:C1205)/A1205</f>
+        <v>12.49860665875234</v>
+      </c>
+    </row>
+    <row r="1206" spans="1:4">
+      <c r="A1206" s="17">
+        <f t="shared" si="8"/>
+        <v>1204</v>
+      </c>
+      <c r="B1206" s="37">
+        <v>46111</v>
+      </c>
+      <c r="C1206" s="38">
+        <v>15.18000031</v>
+      </c>
+      <c r="D1206" s="17">
+        <f>SUM(C$3:C1206)/A1206</f>
+        <v>12.50083372989125</v>
+      </c>
+    </row>
+    <row r="1207" spans="1:4">
+      <c r="A1207" s="17">
+        <f t="shared" si="8"/>
+        <v>1205</v>
+      </c>
+      <c r="B1207" s="37">
+        <v>46112</v>
+      </c>
+      <c r="C1207" s="38">
+        <v>15.079999920000001</v>
+      </c>
+      <c r="D1207" s="17">
+        <f>SUM(C$3:C1207)/A1207</f>
+        <v>12.502974116771009</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4445,7 +4445,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -5003,6 +5003,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5012,7 +5015,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5570,6 +5573,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>372000</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>374000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5612,7 +5618,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -6170,6 +6176,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6179,7 +6188,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6737,6 +6746,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>615439.812291938</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>583459.30829098867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6779,7 +6791,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7337,6 +7349,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>46080</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>46112</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7346,7 +7361,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="186"/>
+                <c:ptCount val="187"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7904,6 +7919,9 @@
                 </c:pt>
                 <c:pt idx="185">
                   <c:v>243439.812291938</c:v>
+                </c:pt>
+                <c:pt idx="186">
+                  <c:v>209459.30829098867</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7925,11 +7943,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="480350208"/>
-        <c:axId val="480351744"/>
+        <c:axId val="393921280"/>
+        <c:axId val="393922816"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="480350208"/>
+        <c:axId val="393921280"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7972,14 +7990,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480351744"/>
+        <c:crossAx val="393922816"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="480351744"/>
+        <c:axId val="393922816"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8030,7 +8048,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="480350208"/>
+        <c:crossAx val="393921280"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8436,7 +8454,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB188"/>
+  <dimension ref="A1:AB189"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16393,6 +16411,39 @@
       <c r="J188" s="31">
         <f>VLOOKUP(A188,myPEPB!B:C,2)</f>
         <v>15.64000034</v>
+      </c>
+    </row>
+    <row r="189" spans="1:10" ht="12.75">
+      <c r="A189" s="13">
+        <v>46112</v>
+      </c>
+      <c r="B189" s="14">
+        <v>2.8264689941406251</v>
+      </c>
+      <c r="C189" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D189" s="16">
+        <v>707.59665297799972</v>
+      </c>
+      <c r="E189" s="16">
+        <v>206426.92684778126</v>
+      </c>
+      <c r="F189" s="16">
+        <v>583459.30829098867</v>
+      </c>
+      <c r="G189" s="16">
+        <v>374000</v>
+      </c>
+      <c r="H189" s="16">
+        <v>583459.30829098867</v>
+      </c>
+      <c r="I189" s="16">
+        <v>209459.30829098867</v>
+      </c>
+      <c r="J189" s="31">
+        <f>VLOOKUP(A189,myPEPB!B:C,2)</f>
+        <v>15.079999920000001</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="961" uniqueCount="956">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="975">
   <si>
     <t>PE</t>
   </si>
@@ -3831,6 +3831,82 @@
   </si>
   <si>
     <t xml:space="preserve">2026/3/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/28
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/4/23
 </t>
   </si>
 </sst>
@@ -7943,11 +8019,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="393921280"/>
-        <c:axId val="393922816"/>
+        <c:axId val="437157888"/>
+        <c:axId val="465683584"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="393921280"/>
+        <c:axId val="437157888"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -7990,14 +8066,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393922816"/>
+        <c:crossAx val="465683584"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="393922816"/>
+        <c:axId val="465683584"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8048,7 +8124,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="393921280"/>
+        <c:crossAx val="437157888"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16459,7 +16535,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1207"/>
+  <dimension ref="A1:D1228"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -34502,7 +34578,7 @@
     </row>
     <row r="1129" spans="1:4">
       <c r="A1129" s="17">
-        <f t="shared" ref="A1129:A1207" si="8">A1128+1</f>
+        <f t="shared" ref="A1129:A1223" si="8">A1128+1</f>
         <v>1127</v>
       </c>
       <c r="B1129" s="37">
@@ -35762,6 +35838,342 @@
       <c r="D1207" s="17">
         <f>SUM(C$3:C1207)/A1207</f>
         <v>12.502974116771009</v>
+      </c>
+    </row>
+    <row r="1208" spans="1:4">
+      <c r="A1208" s="17">
+        <f t="shared" si="8"/>
+        <v>1206</v>
+      </c>
+      <c r="B1208" s="37" t="s">
+        <v>956</v>
+      </c>
+      <c r="C1208" s="38">
+        <v>15.079999920000001</v>
+      </c>
+      <c r="D1208" s="17">
+        <f>SUM(C$3:C1208)/A1208</f>
+        <v>12.505110954087121</v>
+      </c>
+    </row>
+    <row r="1209" spans="1:4">
+      <c r="A1209" s="17">
+        <f t="shared" si="8"/>
+        <v>1207</v>
+      </c>
+      <c r="B1209" s="37" t="s">
+        <v>957</v>
+      </c>
+      <c r="C1209" s="38">
+        <v>15.19999981</v>
+      </c>
+      <c r="D1209" s="17">
+        <f>SUM(C$3:C1209)/A1209</f>
+        <v>12.507343670620601</v>
+      </c>
+    </row>
+    <row r="1210" spans="1:4">
+      <c r="A1210" s="17">
+        <f t="shared" si="8"/>
+        <v>1208</v>
+      </c>
+      <c r="B1210" s="37" t="s">
+        <v>958</v>
+      </c>
+      <c r="C1210" s="38">
+        <v>15.06999969</v>
+      </c>
+      <c r="D1210" s="17">
+        <f>SUM(C$3:C1210)/A1210</f>
+        <v>12.509465074610155</v>
+      </c>
+    </row>
+    <row r="1211" spans="1:4">
+      <c r="A1211" s="17">
+        <f t="shared" si="8"/>
+        <v>1209</v>
+      </c>
+      <c r="B1211" s="37" t="s">
+        <v>959</v>
+      </c>
+      <c r="C1211" s="38">
+        <v>15.06000042</v>
+      </c>
+      <c r="D1211" s="17">
+        <f>SUM(C$3:C1211)/A1211</f>
+        <v>12.511574698551751</v>
+      </c>
+    </row>
+    <row r="1212" spans="1:4">
+      <c r="A1212" s="17">
+        <f t="shared" si="8"/>
+        <v>1210</v>
+      </c>
+      <c r="B1212" s="37" t="s">
+        <v>960</v>
+      </c>
+      <c r="C1212" s="38">
+        <v>15.43000031</v>
+      </c>
+      <c r="D1212" s="17">
+        <f>SUM(C$3:C1212)/A1212</f>
+        <v>12.513986620544683</v>
+      </c>
+    </row>
+    <row r="1213" spans="1:4">
+      <c r="A1213" s="17">
+        <f t="shared" si="8"/>
+        <v>1211</v>
+      </c>
+      <c r="B1213" s="37" t="s">
+        <v>961</v>
+      </c>
+      <c r="C1213" s="38">
+        <v>15.35999966</v>
+      </c>
+      <c r="D1213" s="17">
+        <f>SUM(C$3:C1213)/A1213</f>
+        <v>12.51633675517677</v>
+      </c>
+    </row>
+    <row r="1214" spans="1:4">
+      <c r="A1214" s="17">
+        <f t="shared" si="8"/>
+        <v>1212</v>
+      </c>
+      <c r="B1214" s="37" t="s">
+        <v>962</v>
+      </c>
+      <c r="C1214" s="38">
+        <v>15.52000046</v>
+      </c>
+      <c r="D1214" s="17">
+        <f>SUM(C$3:C1214)/A1214</f>
+        <v>12.518815025560286</v>
+      </c>
+    </row>
+    <row r="1215" spans="1:4">
+      <c r="A1215" s="17">
+        <f t="shared" si="8"/>
+        <v>1213</v>
+      </c>
+      <c r="B1215" s="37" t="s">
+        <v>963</v>
+      </c>
+      <c r="C1215" s="38">
+        <v>15.539999959999999</v>
+      </c>
+      <c r="D1215" s="17">
+        <f>SUM(C$3:C1215)/A1215</f>
+        <v>12.521305697394119</v>
+      </c>
+    </row>
+    <row r="1216" spans="1:4">
+      <c r="A1216" s="17">
+        <f t="shared" si="8"/>
+        <v>1214</v>
+      </c>
+      <c r="B1216" s="37" t="s">
+        <v>964</v>
+      </c>
+      <c r="C1216" s="38">
+        <v>15.68999958</v>
+      </c>
+      <c r="D1216" s="17">
+        <f>SUM(C$3:C1216)/A1216</f>
+        <v>12.523915824150796</v>
+      </c>
+    </row>
+    <row r="1217" spans="1:4">
+      <c r="A1217" s="17">
+        <f t="shared" si="8"/>
+        <v>1215</v>
+      </c>
+      <c r="B1217" s="37" t="s">
+        <v>965</v>
+      </c>
+      <c r="C1217" s="38">
+        <v>15.68000031</v>
+      </c>
+      <c r="D1217" s="17">
+        <f>SUM(C$3:C1217)/A1217</f>
+        <v>12.526513424550672</v>
+      </c>
+    </row>
+    <row r="1218" spans="1:4">
+      <c r="A1218" s="17">
+        <f t="shared" si="8"/>
+        <v>1216</v>
+      </c>
+      <c r="B1218" s="37" t="s">
+        <v>966</v>
+      </c>
+      <c r="C1218" s="38">
+        <v>15.80000019</v>
+      </c>
+      <c r="D1218" s="17">
+        <f>SUM(C$3:C1218)/A1218</f>
+        <v>12.52920543669331</v>
+      </c>
+    </row>
+    <row r="1219" spans="1:4">
+      <c r="A1219" s="17">
+        <f t="shared" si="8"/>
+        <v>1217</v>
+      </c>
+      <c r="B1219" s="37" t="s">
+        <v>967</v>
+      </c>
+      <c r="C1219" s="38">
+        <v>15.72999954</v>
+      </c>
+      <c r="D1219" s="17">
+        <f>SUM(C$3:C1219)/A1219</f>
+        <v>12.531835505800384</v>
+      </c>
+    </row>
+    <row r="1220" spans="1:4">
+      <c r="A1220" s="17">
+        <f t="shared" si="8"/>
+        <v>1218</v>
+      </c>
+      <c r="B1220" s="37" t="s">
+        <v>968</v>
+      </c>
+      <c r="C1220" s="38">
+        <v>15.829999920000001</v>
+      </c>
+      <c r="D1220" s="17">
+        <f>SUM(C$3:C1220)/A1220</f>
+        <v>12.534543358357197</v>
+      </c>
+    </row>
+    <row r="1221" spans="1:4">
+      <c r="A1221" s="17">
+        <f t="shared" si="8"/>
+        <v>1219</v>
+      </c>
+      <c r="B1221" s="37" t="s">
+        <v>969</v>
+      </c>
+      <c r="C1221" s="38">
+        <v>15.89000034</v>
+      </c>
+      <c r="D1221" s="17">
+        <f>SUM(C$3:C1221)/A1221</f>
+        <v>12.537295989187093</v>
+      </c>
+    </row>
+    <row r="1222" spans="1:4">
+      <c r="A1222" s="17">
+        <f t="shared" si="8"/>
+        <v>1220</v>
+      </c>
+      <c r="B1222" s="37" t="s">
+        <v>970</v>
+      </c>
+      <c r="C1222" s="38">
+        <v>15.97000027</v>
+      </c>
+      <c r="D1222" s="17">
+        <f>SUM(C$3:C1222)/A1222</f>
+        <v>12.540109681220546</v>
+      </c>
+    </row>
+    <row r="1223" spans="1:4">
+      <c r="A1223" s="17">
+        <f t="shared" si="8"/>
+        <v>1221</v>
+      </c>
+      <c r="B1223" s="37" t="s">
+        <v>974</v>
+      </c>
+      <c r="C1223" s="38">
+        <v>15.93</v>
+      </c>
+      <c r="D1223" s="17">
+        <f>SUM(C$3:C1223)/A1223</f>
+        <v>12.542886004167949</v>
+      </c>
+    </row>
+    <row r="1224" spans="1:4">
+      <c r="A1224" s="17">
+        <f t="shared" ref="A1224:A1228" si="9">A1223+1</f>
+        <v>1222</v>
+      </c>
+      <c r="B1224" s="37" t="s">
+        <v>971</v>
+      </c>
+      <c r="C1224" s="38">
+        <v>15.920000079999999</v>
+      </c>
+      <c r="D1224" s="17">
+        <f>SUM(C$3:C1224)/A1224</f>
+        <v>12.545649599974686</v>
+      </c>
+    </row>
+    <row r="1225" spans="1:4">
+      <c r="A1225" s="17">
+        <f t="shared" si="9"/>
+        <v>1223</v>
+      </c>
+      <c r="B1225" s="37" t="s">
+        <v>972</v>
+      </c>
+      <c r="C1225" s="38">
+        <v>15.899999619999999</v>
+      </c>
+      <c r="D1225" s="17">
+        <f>SUM(C$3:C1225)/A1225</f>
+        <v>12.548392322803815</v>
+      </c>
+    </row>
+    <row r="1226" spans="1:4">
+      <c r="A1226" s="17">
+        <f t="shared" si="9"/>
+        <v>1224</v>
+      </c>
+      <c r="B1226" s="37" t="s">
+        <v>973</v>
+      </c>
+      <c r="C1226" s="38">
+        <v>15.880000109999999</v>
+      </c>
+      <c r="D1226" s="17">
+        <f>SUM(C$3:C1226)/A1226</f>
+        <v>12.551114224590741</v>
+      </c>
+    </row>
+    <row r="1227" spans="1:4">
+      <c r="A1227" s="17">
+        <f t="shared" si="9"/>
+        <v>1225</v>
+      </c>
+      <c r="B1227" s="37">
+        <v>46141</v>
+      </c>
+      <c r="C1227" s="38">
+        <v>16.020000459999999</v>
+      </c>
+      <c r="D1227" s="17">
+        <f>SUM(C$3:C1227)/A1227</f>
+        <v>12.553945968456381</v>
+      </c>
+    </row>
+    <row r="1228" spans="1:4">
+      <c r="A1228" s="17">
+        <f t="shared" si="9"/>
+        <v>1226</v>
+      </c>
+      <c r="B1228" s="37">
+        <v>46142</v>
+      </c>
+      <c r="C1228" s="38">
+        <v>15.90999985</v>
+      </c>
+      <c r="D1228" s="17">
+        <f>SUM(C$3:C1228)/A1228</f>
+        <v>12.556683369664817</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4521,7 +4521,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -5082,6 +5082,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5091,7 +5094,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5652,6 +5655,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>374000</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>376000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5694,7 +5700,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -6255,6 +6261,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6264,7 +6273,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6825,6 +6834,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>583459.30829098867</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>628481.38113592926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6867,7 +6879,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7428,6 +7440,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>46112</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>46142</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7437,7 +7452,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="187"/>
+                <c:ptCount val="188"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -7998,6 +8013,9 @@
                 </c:pt>
                 <c:pt idx="186">
                   <c:v>209459.30829098867</c:v>
+                </c:pt>
+                <c:pt idx="187">
+                  <c:v>252481.38113592926</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8019,11 +8037,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="437157888"/>
-        <c:axId val="465683584"/>
+        <c:axId val="401427840"/>
+        <c:axId val="404499456"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="437157888"/>
+        <c:axId val="401427840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8066,14 +8084,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="465683584"/>
+        <c:crossAx val="404499456"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="465683584"/>
+        <c:axId val="404499456"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8124,7 +8142,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="437157888"/>
+        <c:crossAx val="401427840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8530,7 +8548,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB189"/>
+  <dimension ref="A1:AB190"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16520,6 +16538,39 @@
       <c r="J189" s="31">
         <f>VLOOKUP(A189,myPEPB!B:C,2)</f>
         <v>15.079999920000001</v>
+      </c>
+    </row>
+    <row r="190" spans="1:10" ht="12.75">
+      <c r="A190" s="13">
+        <v>46142</v>
+      </c>
+      <c r="B190" s="14">
+        <v>3.0348820800781251</v>
+      </c>
+      <c r="C190" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D190" s="16">
+        <v>659.00418771740715</v>
+      </c>
+      <c r="E190" s="16">
+        <v>207085.93103549865</v>
+      </c>
+      <c r="F190" s="16">
+        <v>628481.38113592926</v>
+      </c>
+      <c r="G190" s="16">
+        <v>376000</v>
+      </c>
+      <c r="H190" s="16">
+        <v>628481.38113592926</v>
+      </c>
+      <c r="I190" s="16">
+        <v>252481.38113592926</v>
+      </c>
+      <c r="J190" s="31">
+        <f>VLOOKUP(A190,myPEPB!B:C,2)</f>
+        <v>15.90999985</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="980" uniqueCount="975">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="991">
   <si>
     <t>PE</t>
   </si>
@@ -3907,6 +3907,70 @@
   </si>
   <si>
     <t xml:space="preserve">2026/4/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/6
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/7
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/13
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/14
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/19
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/20
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/21
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/26
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/5/27
 </t>
   </si>
 </sst>
@@ -8037,11 +8101,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="401427840"/>
-        <c:axId val="404499456"/>
+        <c:axId val="162924800"/>
+        <c:axId val="390036096"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="401427840"/>
+        <c:axId val="162924800"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8084,14 +8148,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="404499456"/>
+        <c:crossAx val="390036096"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="404499456"/>
+        <c:axId val="390036096"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8142,7 +8206,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="401427840"/>
+        <c:crossAx val="162924800"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16586,7 +16650,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1228"/>
+  <dimension ref="A1:D1246"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -36149,7 +36213,7 @@
     </row>
     <row r="1224" spans="1:4">
       <c r="A1224" s="17">
-        <f t="shared" ref="A1224:A1228" si="9">A1223+1</f>
+        <f t="shared" ref="A1224:A1246" si="9">A1223+1</f>
         <v>1222</v>
       </c>
       <c r="B1224" s="37" t="s">
@@ -36225,6 +36289,294 @@
       <c r="D1228" s="17">
         <f>SUM(C$3:C1228)/A1228</f>
         <v>12.556683369664817</v>
+      </c>
+    </row>
+    <row r="1229" spans="1:4">
+      <c r="A1229" s="17">
+        <f t="shared" si="9"/>
+        <v>1227</v>
+      </c>
+      <c r="B1229" s="37" t="s">
+        <v>975</v>
+      </c>
+      <c r="C1229" s="38">
+        <v>16.200000760000002</v>
+      </c>
+      <c r="D1229" s="17">
+        <f>SUM(C$3:C1229)/A1229</f>
+        <v>12.559652658491496</v>
+      </c>
+    </row>
+    <row r="1230" spans="1:4">
+      <c r="A1230" s="17">
+        <f t="shared" si="9"/>
+        <v>1228</v>
+      </c>
+      <c r="B1230" s="37" t="s">
+        <v>976</v>
+      </c>
+      <c r="C1230" s="38">
+        <v>16.209999079999999</v>
+      </c>
+      <c r="D1230" s="17">
+        <f>SUM(C$3:C1230)/A1230</f>
+        <v>12.562625253297284</v>
+      </c>
+    </row>
+    <row r="1231" spans="1:4">
+      <c r="A1231" s="17">
+        <f t="shared" si="9"/>
+        <v>1229</v>
+      </c>
+      <c r="B1231" s="37" t="s">
+        <v>977</v>
+      </c>
+      <c r="C1231" s="38">
+        <v>16.149999619999999</v>
+      </c>
+      <c r="D1231" s="17">
+        <f>SUM(C$3:C1231)/A1231</f>
+        <v>12.565544190943097</v>
+      </c>
+    </row>
+    <row r="1232" spans="1:4">
+      <c r="A1232" s="17">
+        <f t="shared" si="9"/>
+        <v>1230</v>
+      </c>
+      <c r="B1232" s="37" t="s">
+        <v>978</v>
+      </c>
+      <c r="C1232" s="38">
+        <v>16.340000150000002</v>
+      </c>
+      <c r="D1232" s="17">
+        <f>SUM(C$3:C1232)/A1232</f>
+        <v>12.568612854324444</v>
+      </c>
+    </row>
+    <row r="1233" spans="1:4">
+      <c r="A1233" s="17">
+        <f t="shared" si="9"/>
+        <v>1231</v>
+      </c>
+      <c r="B1233" s="37" t="s">
+        <v>979</v>
+      </c>
+      <c r="C1233" s="38">
+        <v>16.270000459999999</v>
+      </c>
+      <c r="D1233" s="17">
+        <f>SUM(C$3:C1233)/A1233</f>
+        <v>12.571619667976494</v>
+      </c>
+    </row>
+    <row r="1234" spans="1:4">
+      <c r="A1234" s="17">
+        <f t="shared" si="9"/>
+        <v>1232</v>
+      </c>
+      <c r="B1234" s="37" t="s">
+        <v>980</v>
+      </c>
+      <c r="C1234" s="38">
+        <v>16.38999939</v>
+      </c>
+      <c r="D1234" s="17">
+        <f>SUM(C$3:C1234)/A1234</f>
+        <v>12.574719002166448</v>
+      </c>
+    </row>
+    <row r="1235" spans="1:4">
+      <c r="A1235" s="17">
+        <f t="shared" si="9"/>
+        <v>1233</v>
+      </c>
+      <c r="B1235" s="37" t="s">
+        <v>981</v>
+      </c>
+      <c r="C1235" s="38">
+        <v>16.170000080000001</v>
+      </c>
+      <c r="D1235" s="17">
+        <f>SUM(C$3:C1235)/A1235</f>
+        <v>12.577634883008161</v>
+      </c>
+    </row>
+    <row r="1236" spans="1:4">
+      <c r="A1236" s="17">
+        <f t="shared" si="9"/>
+        <v>1234</v>
+      </c>
+      <c r="B1236" s="37" t="s">
+        <v>982</v>
+      </c>
+      <c r="C1236" s="38">
+        <v>16</v>
+      </c>
+      <c r="D1236" s="17">
+        <f>SUM(C$3:C1236)/A1236</f>
+        <v>12.580408274513017</v>
+      </c>
+    </row>
+    <row r="1237" spans="1:4">
+      <c r="A1237" s="17">
+        <f t="shared" si="9"/>
+        <v>1235</v>
+      </c>
+      <c r="B1237" s="37" t="s">
+        <v>983</v>
+      </c>
+      <c r="C1237" s="38">
+        <v>15.960000040000001</v>
+      </c>
+      <c r="D1237" s="17">
+        <f>SUM(C$3:C1237)/A1237</f>
+        <v>12.583144786064018</v>
+      </c>
+    </row>
+    <row r="1238" spans="1:4">
+      <c r="A1238" s="17">
+        <f t="shared" si="9"/>
+        <v>1236</v>
+      </c>
+      <c r="B1238" s="37" t="s">
+        <v>984</v>
+      </c>
+      <c r="C1238" s="38">
+        <v>16.010000229999999</v>
+      </c>
+      <c r="D1238" s="17">
+        <f>SUM(C$3:C1238)/A1238</f>
+        <v>12.585917322830959</v>
+      </c>
+    </row>
+    <row r="1239" spans="1:4">
+      <c r="A1239" s="17">
+        <f t="shared" si="9"/>
+        <v>1237</v>
+      </c>
+      <c r="B1239" s="37" t="s">
+        <v>985</v>
+      </c>
+      <c r="C1239" s="38">
+        <v>16.010000229999999</v>
+      </c>
+      <c r="D1239" s="17">
+        <f>SUM(C$3:C1239)/A1239</f>
+        <v>12.588685376919212</v>
+      </c>
+    </row>
+    <row r="1240" spans="1:4">
+      <c r="A1240" s="17">
+        <f t="shared" si="9"/>
+        <v>1238</v>
+      </c>
+      <c r="B1240" s="37" t="s">
+        <v>986</v>
+      </c>
+      <c r="C1240" s="38">
+        <v>15.93999958</v>
+      </c>
+      <c r="D1240" s="17">
+        <f>SUM(C$3:C1240)/A1240</f>
+        <v>12.591392415855463</v>
+      </c>
+    </row>
+    <row r="1241" spans="1:4">
+      <c r="A1241" s="17">
+        <f t="shared" si="9"/>
+        <v>1239</v>
+      </c>
+      <c r="B1241" s="37" t="s">
+        <v>987</v>
+      </c>
+      <c r="C1241" s="38">
+        <v>15.84000015</v>
+      </c>
+      <c r="D1241" s="17">
+        <f>SUM(C$3:C1241)/A1241</f>
+        <v>12.594014375285765</v>
+      </c>
+    </row>
+    <row r="1242" spans="1:4">
+      <c r="A1242" s="17">
+        <f t="shared" si="9"/>
+        <v>1240</v>
+      </c>
+      <c r="B1242" s="37" t="s">
+        <v>988</v>
+      </c>
+      <c r="C1242" s="38">
+        <v>15.97000027</v>
+      </c>
+      <c r="D1242" s="17">
+        <f>SUM(C$3:C1242)/A1242</f>
+        <v>12.596736944555696</v>
+      </c>
+    </row>
+    <row r="1243" spans="1:4">
+      <c r="A1243" s="17">
+        <f t="shared" si="9"/>
+        <v>1241</v>
+      </c>
+      <c r="B1243" s="37" t="s">
+        <v>989</v>
+      </c>
+      <c r="C1243" s="38">
+        <v>16.010000229999999</v>
+      </c>
+      <c r="D1243" s="17">
+        <f>SUM(C$3:C1243)/A1243</f>
+        <v>12.599487358162017</v>
+      </c>
+    </row>
+    <row r="1244" spans="1:4">
+      <c r="A1244" s="17">
+        <f t="shared" si="9"/>
+        <v>1242</v>
+      </c>
+      <c r="B1244" s="37" t="s">
+        <v>990</v>
+      </c>
+      <c r="C1244" s="38">
+        <v>15.920000079999999</v>
+      </c>
+      <c r="D1244" s="17">
+        <f>SUM(C$3:C1244)/A1244</f>
+        <v>12.602160878872031</v>
+      </c>
+    </row>
+    <row r="1245" spans="1:4">
+      <c r="A1245" s="17">
+        <f t="shared" si="9"/>
+        <v>1243</v>
+      </c>
+      <c r="B1245" s="37">
+        <v>46170</v>
+      </c>
+      <c r="C1245" s="38">
+        <v>15.920000079999999</v>
+      </c>
+      <c r="D1245" s="17">
+        <f>SUM(C$3:C1245)/A1245</f>
+        <v>12.604830097859262</v>
+      </c>
+    </row>
+    <row r="1246" spans="1:4">
+      <c r="A1246" s="17">
+        <f t="shared" si="9"/>
+        <v>1244</v>
+      </c>
+      <c r="B1246" s="37">
+        <v>46171</v>
+      </c>
+      <c r="C1246" s="38">
+        <v>15.93999958</v>
+      </c>
+      <c r="D1246" s="17">
+        <f>SUM(C$3:C1246)/A1246</f>
+        <v>12.607511102266127</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -4585,7 +4585,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -5149,6 +5149,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5158,7 +5161,7 @@
               <c:f>model1!资金</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -5722,6 +5725,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>376000</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>378000</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -5764,7 +5770,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -6328,6 +6334,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6337,7 +6346,7 @@
               <c:f>model1!资产</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>2000</c:v>
                 </c:pt>
@@ -6901,6 +6910,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>628481.38113592926</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>635142.02797835518</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -6943,7 +6955,7 @@
               <c:f>model1!时间</c:f>
               <c:numCache>
                 <c:formatCode>yyyy\-mm\-dd</c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>40451</c:v>
                 </c:pt>
@@ -7507,6 +7519,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>46142</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>46171</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -7516,7 +7531,7 @@
               <c:f>model1!金额</c:f>
               <c:numCache>
                 <c:formatCode>0.00_ </c:formatCode>
-                <c:ptCount val="188"/>
+                <c:ptCount val="189"/>
                 <c:pt idx="0">
                   <c:v>0</c:v>
                 </c:pt>
@@ -8080,6 +8095,9 @@
                 </c:pt>
                 <c:pt idx="187">
                   <c:v>252481.38113592926</c:v>
+                </c:pt>
+                <c:pt idx="188">
+                  <c:v>257142.02797835518</c:v>
                 </c:pt>
               </c:numCache>
             </c:numRef>
@@ -8101,11 +8119,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="162924800"/>
-        <c:axId val="390036096"/>
+        <c:axId val="99718656"/>
+        <c:axId val="99720576"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="162924800"/>
+        <c:axId val="99718656"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8148,14 +8166,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="390036096"/>
+        <c:crossAx val="99720576"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="390036096"/>
+        <c:axId val="99720576"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8206,7 +8224,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="162924800"/>
+        <c:crossAx val="99718656"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -8612,7 +8630,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:AB190"/>
+  <dimension ref="A1:AB191"/>
   <sheetFormatPr defaultRowHeight="12"/>
   <cols>
     <col min="1" max="1" width="10" style="1" customWidth="1"/>
@@ -16635,6 +16653,39 @@
       <c r="J190" s="31">
         <f>VLOOKUP(A190,myPEPB!B:C,2)</f>
         <v>15.90999985</v>
+      </c>
+    </row>
+    <row r="191" spans="1:10" ht="12.75">
+      <c r="A191" s="13">
+        <v>46171</v>
+      </c>
+      <c r="B191" s="14">
+        <v>3.0573879394531249</v>
+      </c>
+      <c r="C191" s="15">
+        <v>2000</v>
+      </c>
+      <c r="D191" s="16">
+        <v>654.15316590728094</v>
+      </c>
+      <c r="E191" s="16">
+        <v>207740.08420140593</v>
+      </c>
+      <c r="F191" s="16">
+        <v>635142.02797835518</v>
+      </c>
+      <c r="G191" s="16">
+        <v>378000</v>
+      </c>
+      <c r="H191" s="16">
+        <v>635142.02797835518</v>
+      </c>
+      <c r="I191" s="16">
+        <v>257142.02797835518</v>
+      </c>
+      <c r="J191" s="31">
+        <f>VLOOKUP(A191,myPEPB!B:C,2)</f>
+        <v>15.93999958</v>
       </c>
     </row>
   </sheetData>

--- a/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
+++ b/lai/valuationquan/CNIESG300index/CNIESG300indexmodel1.xlsx
@@ -22,7 +22,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="996" uniqueCount="991">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="1015" uniqueCount="1010">
   <si>
     <t>PE</t>
   </si>
@@ -3971,6 +3971,82 @@
   </si>
   <si>
     <t xml:space="preserve">2026/5/27
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/1
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/2
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/3
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/4
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/5
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/8
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/9
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/10
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/11
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/12
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/15
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/16
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/17
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/18
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/22
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/23
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/24
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/25
+</t>
+  </si>
+  <si>
+    <t xml:space="preserve">2026/6/26
 </t>
   </si>
 </sst>
@@ -8119,11 +8195,11 @@
         </c:dLbls>
         <c:marker val="1"/>
         <c:smooth val="0"/>
-        <c:axId val="99718656"/>
-        <c:axId val="99720576"/>
+        <c:axId val="506963840"/>
+        <c:axId val="509047552"/>
       </c:lineChart>
       <c:dateAx>
-        <c:axId val="99718656"/>
+        <c:axId val="506963840"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8166,14 +8242,14 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99720576"/>
+        <c:crossAx val="509047552"/>
         <c:crosses val="autoZero"/>
         <c:auto val="1"/>
         <c:lblOffset val="100"/>
         <c:baseTimeUnit val="days"/>
       </c:dateAx>
       <c:valAx>
-        <c:axId val="99720576"/>
+        <c:axId val="509047552"/>
         <c:scaling>
           <c:orientation val="minMax"/>
         </c:scaling>
@@ -8224,7 +8300,7 @@
             <a:endParaRPr lang="zh-CN"/>
           </a:p>
         </c:txPr>
-        <c:crossAx val="99718656"/>
+        <c:crossAx val="506963840"/>
         <c:crosses val="autoZero"/>
         <c:crossBetween val="between"/>
       </c:valAx>
@@ -16701,7 +16777,7 @@
   <sheetPr codeName="Sheet4">
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:D1246"/>
+  <dimension ref="A1:D1267"/>
   <sheetFormatPr defaultRowHeight="12.75"/>
   <cols>
     <col min="1" max="1" width="9" style="17"/>
@@ -36264,7 +36340,7 @@
     </row>
     <row r="1224" spans="1:4">
       <c r="A1224" s="17">
-        <f t="shared" ref="A1224:A1246" si="9">A1223+1</f>
+        <f t="shared" ref="A1224:A1267" si="9">A1223+1</f>
         <v>1222</v>
       </c>
       <c r="B1224" s="37" t="s">
@@ -36628,6 +36704,342 @@
       <c r="D1246" s="17">
         <f>SUM(C$3:C1246)/A1246</f>
         <v>12.607511102266127</v>
+      </c>
+    </row>
+    <row r="1247" spans="1:4">
+      <c r="A1247" s="17">
+        <f t="shared" si="9"/>
+        <v>1245</v>
+      </c>
+      <c r="B1247" s="37" t="s">
+        <v>991</v>
+      </c>
+      <c r="C1247" s="38">
+        <v>15.89000034</v>
+      </c>
+      <c r="D1247" s="17">
+        <f>SUM(C$3:C1247)/A1247</f>
+        <v>12.610147639806474</v>
+      </c>
+    </row>
+    <row r="1248" spans="1:4">
+      <c r="A1248" s="17">
+        <f t="shared" si="9"/>
+        <v>1246</v>
+      </c>
+      <c r="B1248" s="37" t="s">
+        <v>992</v>
+      </c>
+      <c r="C1248" s="38">
+        <v>16.059999470000001</v>
+      </c>
+      <c r="D1248" s="17">
+        <f>SUM(C$3:C1248)/A1248</f>
+        <v>12.612916381243227</v>
+      </c>
+    </row>
+    <row r="1249" spans="1:4">
+      <c r="A1249" s="17">
+        <f t="shared" si="9"/>
+        <v>1247</v>
+      </c>
+      <c r="B1249" s="37" t="s">
+        <v>993</v>
+      </c>
+      <c r="C1249" s="38">
+        <v>16.079999919999999</v>
+      </c>
+      <c r="D1249" s="17">
+        <f>SUM(C$3:C1249)/A1249</f>
+        <v>12.615696720889384</v>
+      </c>
+    </row>
+    <row r="1250" spans="1:4">
+      <c r="A1250" s="17">
+        <f t="shared" si="9"/>
+        <v>1248</v>
+      </c>
+      <c r="B1250" s="37" t="s">
+        <v>994</v>
+      </c>
+      <c r="C1250" s="38">
+        <v>15.90999985</v>
+      </c>
+      <c r="D1250" s="17">
+        <f>SUM(C$3:C1250)/A1250</f>
+        <v>12.618336386858223</v>
+      </c>
+    </row>
+    <row r="1251" spans="1:4">
+      <c r="A1251" s="17">
+        <f t="shared" si="9"/>
+        <v>1249</v>
+      </c>
+      <c r="B1251" s="37" t="s">
+        <v>995</v>
+      </c>
+      <c r="C1251" s="38">
+        <v>15.710000040000001</v>
+      </c>
+      <c r="D1251" s="17">
+        <f>SUM(C$3:C1251)/A1251</f>
+        <v>12.620811698029675</v>
+      </c>
+    </row>
+    <row r="1252" spans="1:4">
+      <c r="A1252" s="17">
+        <f t="shared" si="9"/>
+        <v>1250</v>
+      </c>
+      <c r="B1252" s="37" t="s">
+        <v>996</v>
+      </c>
+      <c r="C1252" s="38">
+        <v>15.47999954</v>
+      </c>
+      <c r="D1252" s="17">
+        <f>SUM(C$3:C1252)/A1252</f>
+        <v>12.623099048303251</v>
+      </c>
+    </row>
+    <row r="1253" spans="1:4">
+      <c r="A1253" s="17">
+        <f t="shared" si="9"/>
+        <v>1251</v>
+      </c>
+      <c r="B1253" s="37" t="s">
+        <v>997</v>
+      </c>
+      <c r="C1253" s="38">
+        <v>15.65999985</v>
+      </c>
+      <c r="D1253" s="17">
+        <f>SUM(C$3:C1253)/A1253</f>
+        <v>12.625526626881745</v>
+      </c>
+    </row>
+    <row r="1254" spans="1:4">
+      <c r="A1254" s="17">
+        <f t="shared" si="9"/>
+        <v>1252</v>
+      </c>
+      <c r="B1254" s="37" t="s">
+        <v>998</v>
+      </c>
+      <c r="C1254" s="38">
+        <v>15.489999770000001</v>
+      </c>
+      <c r="D1254" s="17">
+        <f>SUM(C$3:C1254)/A1254</f>
+        <v>12.627814544727686</v>
+      </c>
+    </row>
+    <row r="1255" spans="1:4">
+      <c r="A1255" s="17">
+        <f t="shared" si="9"/>
+        <v>1253</v>
+      </c>
+      <c r="B1255" s="37" t="s">
+        <v>999</v>
+      </c>
+      <c r="C1255" s="38">
+        <v>15.43000031</v>
+      </c>
+      <c r="D1255" s="17">
+        <f>SUM(C$3:C1255)/A1255</f>
+        <v>12.630050926024792</v>
+      </c>
+    </row>
+    <row r="1256" spans="1:4">
+      <c r="A1256" s="17">
+        <f t="shared" si="9"/>
+        <v>1254</v>
+      </c>
+      <c r="B1256" s="37" t="s">
+        <v>1000</v>
+      </c>
+      <c r="C1256" s="38">
+        <v>15.630000109999999</v>
+      </c>
+      <c r="D1256" s="17">
+        <f>SUM(C$3:C1256)/A1256</f>
+        <v>12.632443229999254</v>
+      </c>
+    </row>
+    <row r="1257" spans="1:4">
+      <c r="A1257" s="17">
+        <f t="shared" si="9"/>
+        <v>1255</v>
+      </c>
+      <c r="B1257" s="37" t="s">
+        <v>1001</v>
+      </c>
+      <c r="C1257" s="38">
+        <v>16.489999770000001</v>
+      </c>
+      <c r="D1257" s="17">
+        <f>SUM(C$3:C1257)/A1257</f>
+        <v>12.63551698023033</v>
+      </c>
+    </row>
+    <row r="1258" spans="1:4">
+      <c r="A1258" s="17">
+        <f t="shared" si="9"/>
+        <v>1256</v>
+      </c>
+      <c r="B1258" s="37" t="s">
+        <v>1002</v>
+      </c>
+      <c r="C1258" s="38">
+        <v>16.450000760000002</v>
+      </c>
+      <c r="D1258" s="17">
+        <f>SUM(C$3:C1258)/A1258</f>
+        <v>12.638553989609127</v>
+      </c>
+    </row>
+    <row r="1259" spans="1:4">
+      <c r="A1259" s="17">
+        <f t="shared" si="9"/>
+        <v>1257</v>
+      </c>
+      <c r="B1259" s="37" t="s">
+        <v>1003</v>
+      </c>
+      <c r="C1259" s="38">
+        <v>16.489999770000001</v>
+      </c>
+      <c r="D1259" s="17">
+        <f>SUM(C$3:C1259)/A1259</f>
+        <v>12.641617987843327</v>
+      </c>
+    </row>
+    <row r="1260" spans="1:4">
+      <c r="A1260" s="17">
+        <f t="shared" si="9"/>
+        <v>1258</v>
+      </c>
+      <c r="B1260" s="37" t="s">
+        <v>1004</v>
+      </c>
+      <c r="C1260" s="38">
+        <v>16.489999770000001</v>
+      </c>
+      <c r="D1260" s="17">
+        <f>SUM(C$3:C1260)/A1260</f>
+        <v>12.644677114856171</v>
+      </c>
+    </row>
+    <row r="1261" spans="1:4">
+      <c r="A1261" s="17">
+        <f t="shared" si="9"/>
+        <v>1259</v>
+      </c>
+      <c r="B1261" s="37" t="s">
+        <v>1005</v>
+      </c>
+      <c r="C1261" s="38">
+        <v>16.809999470000001</v>
+      </c>
+      <c r="D1261" s="17">
+        <f>SUM(C$3:C1261)/A1261</f>
+        <v>12.647985551992901</v>
+      </c>
+    </row>
+    <row r="1262" spans="1:4">
+      <c r="A1262" s="17">
+        <f t="shared" si="9"/>
+        <v>1260</v>
+      </c>
+      <c r="B1262" s="37" t="s">
+        <v>1006</v>
+      </c>
+      <c r="C1262" s="38">
+        <v>16.38999939</v>
+      </c>
+      <c r="D1262" s="17">
+        <f>SUM(C$3:C1262)/A1262</f>
+        <v>12.650955404245288</v>
+      </c>
+    </row>
+    <row r="1263" spans="1:4">
+      <c r="A1263" s="17">
+        <f t="shared" si="9"/>
+        <v>1261</v>
+      </c>
+      <c r="B1263" s="37" t="s">
+        <v>1007</v>
+      </c>
+      <c r="C1263" s="38">
+        <v>16.420000080000001</v>
+      </c>
+      <c r="D1263" s="17">
+        <f>SUM(C$3:C1263)/A1263</f>
+        <v>12.653944337374355</v>
+      </c>
+    </row>
+    <row r="1264" spans="1:4">
+      <c r="A1264" s="17">
+        <f t="shared" si="9"/>
+        <v>1262</v>
+      </c>
+      <c r="B1264" s="37" t="s">
+        <v>1008</v>
+      </c>
+      <c r="C1264" s="38">
+        <v>16.530000690000001</v>
+      </c>
+      <c r="D1264" s="17">
+        <f>SUM(C$3:C1264)/A1264</f>
+        <v>12.657015697400208</v>
+      </c>
+    </row>
+    <row r="1265" spans="1:4">
+      <c r="A1265" s="17">
+        <f t="shared" si="9"/>
+        <v>1263</v>
+      </c>
+      <c r="B1265" s="37" t="s">
+        <v>1009</v>
+      </c>
+      <c r="C1265" s="38">
+        <v>16.010000229999999</v>
+      </c>
+      <c r="D1265" s="17">
+        <f>SUM(C$3:C1265)/A1265</f>
+        <v>12.659670475335759</v>
+      </c>
+    </row>
+    <row r="1266" spans="1:4">
+      <c r="A1266" s="17">
+        <f t="shared" si="9"/>
+        <v>1264</v>
+      </c>
+      <c r="B1266" s="37">
+        <v>46202</v>
+      </c>
+      <c r="C1266" s="38">
+        <v>16.120000839999999</v>
+      </c>
+      <c r="D1266" s="17">
+        <f>SUM(C$3:C1266)/A1266</f>
+        <v>12.662408078472358</v>
+      </c>
+    </row>
+    <row r="1267" spans="1:4">
+      <c r="A1267" s="17">
+        <f t="shared" si="9"/>
+        <v>1265</v>
+      </c>
+      <c r="B1267" s="37">
+        <v>46203</v>
+      </c>
+      <c r="C1267" s="38">
+        <v>16.190000529999999</v>
+      </c>
+      <c r="D1267" s="17">
+        <f>SUM(C$3:C1267)/A1267</f>
+        <v>12.665196689105978</v>
       </c>
     </row>
   </sheetData>
